--- a/data/holding links.xlsx
+++ b/data/holding links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalva\src\project-hail-mary\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A056BF-94C3-401D-9966-274E91D8FFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0629391-71C9-4760-B74C-7A07164D0E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="6690" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolios" sheetId="1" r:id="rId1"/>
